--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104670_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104670_W24.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.0596</v>
+        <v>8.948</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7753</v>
+        <v>8.1972</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2843</v>
+        <v>0.7508</v>
       </c>
       <c r="G2" t="n">
-        <v>5.3423</v>
+        <v>5.3289</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2295</v>
+        <v>1.2238</v>
       </c>
       <c r="I2" t="n">
-        <v>4.1128</v>
+        <v>4.105</v>
       </c>
       <c r="J2" t="n">
-        <v>5.6103</v>
+        <v>5.5703</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7348</v>
+        <v>1.713</v>
       </c>
       <c r="L2" t="n">
-        <v>3.8755</v>
+        <v>3.8573</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.268</v>
+        <v>-0.2414</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.9217</v>
+        <v>-1.0151</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.113</v>
+        <v>-0.6415</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8087</v>
+        <v>-0.3736</v>
       </c>
       <c r="V2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5373</v>
+        <v>3.8018</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4737</v>
+        <v>4.6797</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9364</v>
+        <v>-0.878</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7202</v>
+        <v>4.7205</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.6264</v>
+        <v>-1.6175</v>
       </c>
       <c r="I3" t="n">
-        <v>6.3466</v>
+        <v>6.3379</v>
       </c>
       <c r="J3" t="n">
-        <v>6.7209</v>
+        <v>6.6962</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6651</v>
+        <v>-0.669</v>
       </c>
       <c r="L3" t="n">
-        <v>7.386</v>
+        <v>7.3652</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0007</v>
+        <v>-1.9758</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1829</v>
+        <v>-0.9187</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.113</v>
+        <v>-0.8784</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0699</v>
+        <v>-0.0403</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8471</v>
+        <v>3.3199</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9196</v>
+        <v>4.1745</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0725</v>
+        <v>-0.8546</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2553</v>
+        <v>0.2375</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1487</v>
+        <v>0.1411</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1065</v>
+        <v>0.0964</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6669</v>
+        <v>1.6265</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4809</v>
+        <v>0.4579</v>
       </c>
       <c r="L4" t="n">
-        <v>1.186</v>
+        <v>1.1686</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4116</v>
+        <v>-1.389</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0472</v>
+        <v>0.4482</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1089</v>
+        <v>0.4177</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1561</v>
+        <v>0.0305</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W4" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9696</v>
+        <v>0.1992</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4904</v>
+        <v>0.1875</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4792</v>
+        <v>0.0117</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2944</v>
+        <v>-1.2851</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.1284</v>
+        <v>-3.125</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8339</v>
+        <v>1.8399</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0602</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.4181</v>
+        <v>-2.4346</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5002</v>
+        <v>2.4949</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3765</v>
+        <v>-1.3453</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7103</v>
+        <v>-0.6904</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9031</v>
+        <v>0.1184</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4083</v>
+        <v>0.1272</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4948</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6584</v>
+        <v>0.0798</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7639</v>
+        <v>-0.2738</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1055</v>
+        <v>0.3536</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1926</v>
+        <v>0.4894</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9695</v>
+        <v>0.6513</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1621</v>
+        <v>-0.1619</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7083</v>
+        <v>1.3176</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5897</v>
+        <v>0.9825</v>
       </c>
       <c r="L6" t="n">
-        <v>1.298</v>
+        <v>0.3351</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5157</v>
+        <v>-0.8282</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3798</v>
+        <v>-0.3312</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1359</v>
+        <v>-0.497</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2654</v>
+        <v>-0.2519</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1897</v>
+        <v>-0.4533</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9243</v>
+        <v>0.2014</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0654</v>
+        <v>-0.3137</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8547</v>
+        <v>0.2518</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7893</v>
+        <v>-0.5655</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4659</v>
+        <v>0.1741</v>
       </c>
       <c r="H7" t="n">
-        <v>0.639</v>
+        <v>-0.9816</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1732</v>
+        <v>1.1557</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3229</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9871</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3359</v>
+        <v>1.2803</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.857</v>
+        <v>-0.4847</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.348</v>
+        <v>-0.3601</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.509</v>
+        <v>-0.1246</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3705</v>
+        <v>0.3042</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0434</v>
+        <v>0.7311</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6729000000000001</v>
+        <v>-0.427</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5717</v>
+        <v>-0.5696</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0522</v>
+        <v>-0.0525</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5717</v>
+        <v>-0.5696</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1573</v>
+        <v>-0.1579</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ALLEN</t>
+          <t>F. MAURI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2886</v>
+        <v>-1.3333</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4084</v>
+        <v>-0.9988</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8802</v>
+        <v>-0.3345</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7062</v>
+        <v>-1.1765</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4775</v>
+        <v>-0.0144</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2287</v>
+        <v>-1.162</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3136</v>
+        <v>-0.7896</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0897</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2239</v>
+        <v>-0.7896</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0198</v>
+        <v>-0.3868</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5672</v>
+        <v>-0.0144</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4526</v>
+        <v>-0.3724</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.323</v>
+        <v>-0.1568</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0907</v>
+        <v>-0.2091</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2323</v>
+        <v>0.0523</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. MAURI</t>
+          <t>M. ALLEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3632</v>
+        <v>-1.7043</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.995</v>
+        <v>-0.9049</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3682</v>
+        <v>-0.7993</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1754</v>
+        <v>-1.7061</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0159</v>
+        <v>-0.485</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1595</v>
+        <v>-1.2211</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7864</v>
+        <v>0.2989</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.0755</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7864</v>
+        <v>0.2234</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3891</v>
+        <v>-2.005</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0159</v>
+        <v>-0.5604</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3732</v>
+        <v>-1.4446</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1878</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2087</v>
+        <v>-0.3812</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0209</v>
+        <v>0.2951</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5292</v>
+        <v>-2.8562</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5488</v>
+        <v>-0.9062</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9804</v>
+        <v>-1.95</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6638</v>
+        <v>-2.6533</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2336</v>
+        <v>0.2409</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.8974</v>
+        <v>-2.8942</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1913</v>
+        <v>-0.2038</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1949</v>
+        <v>1.1893</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3861</v>
+        <v>-1.3931</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.4725</v>
+        <v>-2.4496</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5232</v>
+        <v>0.137</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.747</v>
+        <v>-0.0863</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2238</v>
+        <v>0.2232</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7032</v>
+        <v>-1.7057</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.042</v>
+        <v>-5.0229</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8172</v>
+        <v>-2.5404</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2248</v>
+        <v>-2.4825</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1374</v>
+        <v>-3.1391</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1414</v>
+        <v>-0.1435</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.996</v>
+        <v>-2.9956</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7871</v>
+        <v>-0.8038</v>
       </c>
       <c r="K12" t="n">
-        <v>0.599</v>
+        <v>0.5893</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3861</v>
+        <v>-1.3931</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3503</v>
+        <v>-2.3353</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6099</v>
+        <v>-1.6025</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2296</v>
+        <v>0.2543</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4688</v>
+        <v>-0.1628</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6983</v>
+        <v>0.4171</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.211899999999998</v>
+        <v>4.548700000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>11.7466</v>
+        <v>11.8141</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.5347</v>
+        <v>-7.2654</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4274000000000009</v>
+        <v>0.4207000000000005</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.091</v>
+        <v>-4.092700000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>4.517999999999999</v>
+        <v>4.513300000000003</v>
       </c>
       <c r="J13" t="n">
-        <v>14.6775</v>
+        <v>14.4485</v>
       </c>
       <c r="K13" t="n">
-        <v>1.4308</v>
+        <v>1.2996</v>
       </c>
       <c r="L13" t="n">
-        <v>13.2469</v>
+        <v>13.149</v>
       </c>
       <c r="M13" t="n">
-        <v>-14.2503</v>
+        <v>-14.0279</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.5214</v>
+        <v>-5.3922</v>
       </c>
       <c r="O13" t="n">
-        <v>-8.728999999999999</v>
+        <v>-8.6357</v>
       </c>
       <c r="P13" t="n">
-        <v>3.4026</v>
+        <v>3.4146</v>
       </c>
       <c r="Q13" t="n">
-        <v>-7.939300000000001</v>
+        <v>-7.967300000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>11.3416</v>
+        <v>11.3816</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.739</v>
+        <v>-1.394</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.9659</v>
+        <v>-1.6063</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2267000000000001</v>
+        <v>0.212</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1211</v>
+        <v>2.1074</v>
       </c>
       <c r="W13" t="n">
-        <v>6.973999999999999</v>
+        <v>6.9386</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.8529</v>
+        <v>-4.8312</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3123</v>
+        <v>4.0863</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2874</v>
+        <v>4.496</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0248</v>
+        <v>-0.4096</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5253</v>
+        <v>3.5252</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3824</v>
+        <v>-0.382</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9077</v>
+        <v>3.9072</v>
       </c>
       <c r="J14" t="n">
-        <v>4.8223</v>
+        <v>4.7984</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>4.8885</v>
+        <v>4.878</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2971</v>
+        <v>-1.2731</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5187</v>
+        <v>0.2848</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6956</v>
+        <v>-0.4601</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2143</v>
+        <v>0.7449</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9929</v>
+        <v>3.9238</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1129</v>
+        <v>3.8479</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.12</v>
+        <v>0.0759</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0474</v>
+        <v>3.0587</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0243</v>
+        <v>1.0389</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0231</v>
+        <v>2.0198</v>
       </c>
       <c r="J15" t="n">
-        <v>4.8716</v>
+        <v>4.8473</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5931</v>
+        <v>1.5858</v>
       </c>
       <c r="L15" t="n">
-        <v>3.2785</v>
+        <v>3.2615</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8242</v>
+        <v>-1.7886</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5689</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2554</v>
+        <v>-1.2417</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3312</v>
+        <v>0.2521</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2148</v>
+        <v>-0.019</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1164</v>
+        <v>0.2711</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7735</v>
+        <v>2.1454</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6975</v>
+        <v>1.803</v>
       </c>
       <c r="F16" t="n">
-        <v>0.076</v>
+        <v>0.3424</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6314</v>
+        <v>1.64</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8744</v>
+        <v>0.8786</v>
       </c>
       <c r="I16" t="n">
-        <v>0.757</v>
+        <v>0.7614</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9295</v>
+        <v>1.9238</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6234</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3061</v>
+        <v>1.3033</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2981</v>
+        <v>-0.2838</v>
       </c>
       <c r="N16" t="n">
-        <v>0.251</v>
+        <v>0.2581</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4969</v>
+        <v>-0.1288</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1905</v>
+        <v>-0.0721</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3064</v>
+        <v>-0.0567</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0356</v>
+        <v>-0.3186</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0929</v>
+        <v>-0.6019</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1285</v>
+        <v>0.2833</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.0512</v>
+        <v>-2.0691</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7978</v>
+        <v>-1.8034</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2533</v>
+        <v>-0.2657</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.1273</v>
+        <v>-1.1683</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.6389</v>
+        <v>-1.659</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.4906</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3401</v>
+        <v>0.9977</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0344</v>
+        <v>0.5664</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3058</v>
+        <v>0.4313</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. KUATH</t>
+          <t>L. MANIEMA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1955</v>
+        <v>-0.9621</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7821</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9776</v>
+        <v>-1.0559</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.8038</v>
+        <v>-0.4405</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.114</v>
+        <v>0.1463</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6899</v>
+        <v>-0.5868</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2886</v>
+        <v>0.0172</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3259</v>
+        <v>0.0172</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5152</v>
+        <v>-0.4578</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.788</v>
+        <v>0.129</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7272</v>
+        <v>-0.5868</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3153</v>
+        <v>0.0232</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0707</v>
+        <v>0.0765</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2447</v>
+        <v>-0.0534</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1607</v>
+        <v>-0.5447</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. MANIEMA</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5437</v>
+        <v>-1.7292</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2609</v>
+        <v>-0.4536</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2827</v>
+        <v>-1.2756</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4463</v>
+        <v>-1.943</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1428</v>
+        <v>0.2809</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5891</v>
+        <v>-2.2239</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0173</v>
+        <v>0.046</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0173</v>
+        <v>0.3964</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.3505</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4636</v>
+        <v>-1.989</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1255</v>
+        <v>-0.1155</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5891</v>
+        <v>-1.8734</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5511</v>
+        <v>-0.4204</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2782</v>
+        <v>-0.4509</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2728</v>
+        <v>0.0305</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>K. KUATH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9223</v>
+        <v>-1.7346</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4351</v>
+        <v>0.184</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4872</v>
+        <v>-1.9186</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9546</v>
+        <v>-2.7926</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2711</v>
+        <v>-1.1143</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2257</v>
+        <v>-1.6783</v>
       </c>
       <c r="J20" t="n">
-        <v>0.057</v>
+        <v>-0.301</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3983</v>
+        <v>-0.3382</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3413</v>
+        <v>0.0372</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0116</v>
+        <v>-2.4916</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1272</v>
+        <v>-0.7761</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8844</v>
+        <v>-1.7155</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6067</v>
+        <v>0.7605</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4506</v>
+        <v>0.485</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1561</v>
+        <v>0.2755</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0927</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6073</v>
+        <v>-2.0824</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0639</v>
+        <v>1.2297</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.6713</v>
+        <v>-3.3121</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6394</v>
+        <v>2.6246</v>
       </c>
       <c r="H21" t="n">
-        <v>4.244</v>
+        <v>4.2258</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6046</v>
+        <v>-1.6012</v>
       </c>
       <c r="J21" t="n">
-        <v>5.0795</v>
+        <v>5.0277</v>
       </c>
       <c r="K21" t="n">
-        <v>4.152</v>
+        <v>4.1121</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9275</v>
+        <v>0.9156</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4401</v>
+        <v>-2.4031</v>
       </c>
       <c r="N21" t="n">
-        <v>0.092</v>
+        <v>0.1137</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.5321</v>
+        <v>-2.5168</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5247000000000001</v>
+        <v>0.0245</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5716</v>
+        <v>-0.3349</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0469</v>
+        <v>0.3594</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. METU</t>
+          <t>K. ROBERTSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3518</v>
+        <v>-3.1316</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2402</v>
+        <v>-1.9257</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1116</v>
+        <v>-1.2059</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1825</v>
+        <v>-1.8336</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4719</v>
+        <v>-0.6434</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.6544</v>
+        <v>-1.1903</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4219</v>
+        <v>-0.7037</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1909</v>
+        <v>-0.4277</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.6127</v>
+        <v>-0.276</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7606</v>
+        <v>-1.13</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2811</v>
+        <v>-0.2157</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.0417</v>
+        <v>-0.9143</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5878</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8042</v>
+        <v>0.1754</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1966</v>
+        <v>-0.0838</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6076</v>
+        <v>0.2592</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3856</v>
+        <v>-1.018</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.639</v>
+        <v>-1.018</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. ROBERTSON</t>
+          <t>C. METU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7056</v>
+        <v>-3.6075</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.38</v>
+        <v>-1.4077</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3256</v>
+        <v>-2.1998</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8324</v>
+        <v>-2.1904</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6435999999999999</v>
+        <v>1.4651</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1888</v>
+        <v>-3.6556</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6893</v>
+        <v>-0.4596</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4227</v>
+        <v>1.1646</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.2666</v>
+        <v>-1.6242</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1431</v>
+        <v>-1.7309</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2209</v>
+        <v>0.3005</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9222</v>
+        <v>-2.0314</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4537</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3911</v>
+        <v>0.5634</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5565</v>
+        <v>0.0809</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1654</v>
+        <v>0.4824</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0285</v>
+        <v>-0.387</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0285</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2119</v>
+        <v>-3.4105</v>
       </c>
       <c r="E24" t="n">
-        <v>7.5347</v>
+        <v>7.265500000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.7467</v>
+        <v>-10.6759</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4273</v>
+        <v>-0.4207000000000003</v>
       </c>
       <c r="H24" t="n">
-        <v>4.090699999999999</v>
+        <v>4.092499999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.517999999999999</v>
+        <v>-4.5134</v>
       </c>
       <c r="J24" t="n">
-        <v>14.2501</v>
+        <v>14.0278</v>
       </c>
       <c r="K24" t="n">
-        <v>5.5213</v>
+        <v>5.392</v>
       </c>
       <c r="L24" t="n">
-        <v>8.728899999999999</v>
+        <v>8.635499999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-14.6775</v>
+        <v>-14.4486</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4306</v>
+        <v>-1.2996</v>
       </c>
       <c r="O24" t="n">
-        <v>-13.2468</v>
+        <v>-13.1489</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q24" t="n">
-        <v>-11.3418</v>
+        <v>-11.3817</v>
       </c>
       <c r="R24" t="n">
-        <v>7.939100000000001</v>
+        <v>7.9671</v>
       </c>
       <c r="S24" t="n">
-        <v>1.739</v>
+        <v>2.5324</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2265</v>
+        <v>-0.212</v>
       </c>
       <c r="U24" t="n">
-        <v>1.9658</v>
+        <v>2.7442</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1211</v>
+        <v>-2.1075</v>
       </c>
       <c r="W24" t="n">
-        <v>4.8529</v>
+        <v>4.8313</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.9739</v>
+        <v>-6.9386</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104670_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104670_W24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-4.8312</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.018</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104670_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-6.9386</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
